--- a/20260806_権限設定_03_検証用データセット.xlsx
+++ b/20260806_権限設定_03_検証用データセット.xlsx
@@ -6995,7 +6995,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -7124,22 +7124,22 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>店舗3件を登録</t>
+          <t>権限テンプレート画面を確認（権限を作る前にしか出ない）</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>01_店舗</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>S-02</t>
+          <t>T-04</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr"/>
@@ -7147,17 +7147,17 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>売上・仕入・人件費・費用・予算を検証実施月の1日分として登録</t>
+          <t>店舗3件を登録</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>03_売上／04_仕入／05_人件費／06_費用_予算</t>
+          <t>01_店舗</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -7170,17 +7170,17 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>従業員4名を登録</t>
+          <t>売上・仕入・人件費・費用・予算を検証実施月の1日分として登録</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>02_従業員</t>
+          <t>03_売上／04_仕入／05_人件費／06_費用_予算</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -7193,22 +7193,22 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>検証ユーザー8名を登録</t>
+          <t>従業員4名を登録</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>07_検証ユーザー</t>
+          <t>02_従業員</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>S-03</t>
+          <t>S-02</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr"/>
@@ -7216,22 +7216,22 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>権限7件を作成</t>
+          <t>検証ユーザー8名を登録</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>08_権限設定値</t>
+          <t>07_検証ユーザー</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>S-04</t>
+          <t>S-03</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr"/>
@@ -7239,22 +7239,22 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>割当と担当店舗を設定</t>
+          <t>権限7件を作成</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>07_検証ユーザー</t>
+          <t>08_権限設定値</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>S-05</t>
+          <t>S-04</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr"/>
@@ -7262,64 +7262,87 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>割当と担当店舗を設定</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>07_検証ユーザー</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>S-05</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>指標の初期値を突合（投入ではなく確認）</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>09_指標の初期値</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t>T-19</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="E25" s="4" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>■ 注意</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>日付は 2026-08-01 で作成しています。検証実施月に合わせて置換してください。</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>実顧客のデータは使わないでください。検証で権限を絞る操作をするため、実データだと事故ります。</t>
+          <t>日付は 2026-08-01 で作成しています。検証実施月に合わせて置換してください。</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>投入できない場合、T-11・T-23 は「検証不能」として記録してください。「問題なし」と書いてはいけません。</t>
+          <t>実顧客のデータは使わないでください。検証で権限を絞る操作をするため、実データだと事故ります。</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
+          <t>投入できない場合、T-11・T-23 は「検証不能」として記録してください。「問題なし」と書いてはいけません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
           <t>指標の既定は雛形で決まります。08 のベース列と 09 の期待値は必ず対応させてください。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="E18:E24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E18:E25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"済,未,対象外"</formula1>
     </dataValidation>
   </dataValidations>

--- a/20260806_権限設定_03_検証用データセット.xlsx
+++ b/20260806_権限設定_03_検証用データセット.xlsx
@@ -604,7 +604,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>T-09 T-10 T-11 T-18</t>
+          <t>T-11</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>T-10 T-11 T-23</t>
+          <t>S-02 T-10 T-11 T-23</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>T-12 T-23</t>
+          <t>S-02 T-12</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -700,7 +700,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>T-09 T-12</t>
+          <t>S-02</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>T-13 T-23</t>
+          <t>S-02 T-13</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>S-03 S-05 T-09〜T-18</t>
+          <t>S-03 S-05 T-06 T-09 T-09b T-10 T-11 T-12 T-13 T-14 T-15 T-16 T-18 T-23</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>S-04 T-05</t>
+          <t>S-04 T-05 T-09 T-09b T-10</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>T-19</t>
+          <t>T-19 T-23</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">

--- a/20260806_権限設定_03_検証用データセット.xlsx
+++ b/20260806_権限設定_03_検証用データセット.xlsx
@@ -572,7 +572,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>S-02</t>
+          <t>S-02 T-26</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>S-03 S-05 T-06 T-09 T-09b T-10 T-11 T-12 T-13 T-14 T-15 T-16 T-18 T-23</t>
+          <t>S-03 S-05 T-06 T-09 T-09b T-10 T-11 T-12 T-13 T-14 T-15 T-16 T-18 T-25 T-26 T-23</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>S-04 T-05 T-09 T-09b T-10</t>
+          <t>S-04 T-05 T-09 T-09b T-10 T-25 T-27</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
